--- a/data/배출계수_통합_DB.xlsx
+++ b/data/배출계수_통합_DB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Scope3_AI\Scope3_AI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756B389A-50CE-4FEA-B025-EB7A612F6EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E3AE0E-A335-4757-A40D-D421BF152762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="에너지" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="2939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="2940">
   <si>
     <t>C1/C2 구매 배출계수 매핑 DB  |  US EPA Supply Chain GHG Emission Factors v1.3 (NAICS 기반)  |  한국 기업 구매 품목 → NAICS 매핑</t>
   </si>
@@ -9359,6 +9359,57 @@
     <t>환경성적표지</t>
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>콘크리트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시멘트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아스콘</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -9371,7 +9422,7 @@
     <numFmt numFmtId="179" formatCode="0.000000000"/>
     <numFmt numFmtId="180" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9586,6 +9637,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="3"/>
       <charset val="129"/>
@@ -9941,7 +10006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10616,6 +10681,9 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="47" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10653,8 +10721,8 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10930,47 +10998,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="236" t="s">
         <v>2936</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
-      <c r="I1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="233" t="s">
+      <c r="A2" s="234" t="s">
         <v>767</v>
       </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="232"/>
-      <c r="I2" s="232"/>
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
+      <c r="H2" s="233"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A3" s="234" t="s">
+      <c r="A3" s="235" t="s">
         <v>768</v>
       </c>
-      <c r="B3" s="232"/>
-      <c r="C3" s="232"/>
-      <c r="D3" s="232"/>
-      <c r="E3" s="237" t="s">
+      <c r="B3" s="233"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="238" t="s">
         <v>769</v>
       </c>
-      <c r="F3" s="232"/>
-      <c r="G3" s="236" t="s">
+      <c r="F3" s="233"/>
+      <c r="G3" s="237" t="s">
         <v>770</v>
       </c>
-      <c r="H3" s="232"/>
-      <c r="I3" s="232"/>
+      <c r="H3" s="233"/>
+      <c r="I3" s="233"/>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -11411,17 +11479,17 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.75" customHeight="1">
-      <c r="A19" s="231" t="s">
+      <c r="A19" s="232" t="s">
         <v>806</v>
       </c>
-      <c r="B19" s="232"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="232"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="232"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="232"/>
-      <c r="I19" s="232"/>
+      <c r="B19" s="233"/>
+      <c r="C19" s="233"/>
+      <c r="D19" s="233"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="233"/>
+      <c r="G19" s="233"/>
+      <c r="H19" s="233"/>
+      <c r="I19" s="233"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1"/>
     <row r="21" spans="1:10" ht="16.5" customHeight="1"/>
@@ -12433,15 +12501,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="240" t="s">
         <v>1307</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
     </row>
     <row r="2" spans="1:7" ht="39.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -12536,15 +12604,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A6" s="231" t="s">
+      <c r="A6" s="232" t="s">
         <v>1324</v>
       </c>
-      <c r="B6" s="232"/>
-      <c r="C6" s="232"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
+      <c r="B6" s="233"/>
+      <c r="C6" s="233"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
     </row>
     <row r="7" spans="1:7" ht="16.5" customHeight="1"/>
     <row r="8" spans="1:7" ht="16.5" customHeight="1"/>
@@ -23562,7 +23630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -23573,20 +23641,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="230" t="s">
+      <c r="A1" s="231" t="s">
         <v>2926</v>
       </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="230"/>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="225" t="s">
@@ -23632,15 +23700,15 @@
         <v>2</v>
       </c>
       <c r="B5" s="228" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C5" s="227" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D5" s="227">
-        <v>0.19527</v>
-      </c>
-      <c r="E5" s="243" t="s">
+        <v>0.27229999999999999</v>
+      </c>
+      <c r="E5" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23649,15 +23717,15 @@
         <v>3</v>
       </c>
       <c r="B6" s="228" t="s">
-        <v>784</v>
+        <v>797</v>
       </c>
       <c r="C6" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D6" s="227">
-        <v>0.27229999999999999</v>
-      </c>
-      <c r="E6" s="243" t="s">
+        <v>8.3169999999999994E-2</v>
+      </c>
+      <c r="E6" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23666,15 +23734,15 @@
         <v>4</v>
       </c>
       <c r="B7" s="228" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C7" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D7" s="227">
-        <v>8.3169999999999994E-2</v>
-      </c>
-      <c r="E7" s="243" t="s">
+        <v>6.8190000000000001E-2</v>
+      </c>
+      <c r="E7" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23683,15 +23751,15 @@
         <v>5</v>
       </c>
       <c r="B8" s="228" t="s">
-        <v>792</v>
+        <v>1423</v>
       </c>
       <c r="C8" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D8" s="227">
-        <v>6.8190000000000001E-2</v>
-      </c>
-      <c r="E8" s="243" t="s">
+        <v>0.25290000000000001</v>
+      </c>
+      <c r="E8" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23700,15 +23768,15 @@
         <v>6</v>
       </c>
       <c r="B9" s="228" t="s">
-        <v>1423</v>
+        <v>790</v>
       </c>
       <c r="C9" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D9" s="227">
-        <v>0.25290000000000001</v>
-      </c>
-      <c r="E9" s="243" t="s">
+        <v>0.39360000000000001</v>
+      </c>
+      <c r="E9" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23717,15 +23785,15 @@
         <v>7</v>
       </c>
       <c r="B10" s="228" t="s">
-        <v>790</v>
+        <v>1450</v>
       </c>
       <c r="C10" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D10" s="227">
-        <v>0.39360000000000001</v>
-      </c>
-      <c r="E10" s="243" t="s">
+        <v>4.113E-2</v>
+      </c>
+      <c r="E10" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23734,15 +23802,15 @@
         <v>8</v>
       </c>
       <c r="B11" s="228" t="s">
-        <v>1450</v>
+        <v>2932</v>
       </c>
       <c r="C11" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D11" s="227">
-        <v>4.113E-2</v>
-      </c>
-      <c r="E11" s="243" t="s">
+        <v>0.2394</v>
+      </c>
+      <c r="E11" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23751,15 +23819,15 @@
         <v>9</v>
       </c>
       <c r="B12" s="228" t="s">
-        <v>2932</v>
+        <v>2186</v>
       </c>
       <c r="C12" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D12" s="227">
-        <v>0.2394</v>
-      </c>
-      <c r="E12" s="243" t="s">
+        <v>0.3246</v>
+      </c>
+      <c r="E12" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
@@ -23768,58 +23836,41 @@
         <v>10</v>
       </c>
       <c r="B13" s="228" t="s">
-        <v>2186</v>
+        <v>1513</v>
       </c>
       <c r="C13" s="227" t="s">
         <v>785</v>
       </c>
       <c r="D13" s="227">
-        <v>0.3246</v>
-      </c>
-      <c r="E13" s="243" t="s">
+        <v>0.47949999999999998</v>
+      </c>
+      <c r="E13" s="230" t="s">
         <v>2938</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" ht="24">
       <c r="A14" s="227">
         <v>11</v>
       </c>
       <c r="B14" s="228" t="s">
-        <v>1513</v>
+        <v>2933</v>
       </c>
       <c r="C14" s="227" t="s">
-        <v>785</v>
+        <v>2934</v>
       </c>
       <c r="D14" s="227">
-        <v>0.47949999999999998</v>
-      </c>
-      <c r="E14" s="243" t="s">
-        <v>2938</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="24">
-      <c r="A15" s="227">
-        <v>12</v>
-      </c>
-      <c r="B15" s="228" t="s">
-        <v>2933</v>
-      </c>
-      <c r="C15" s="227" t="s">
-        <v>2934</v>
-      </c>
-      <c r="D15" s="227">
         <v>4.8444911450000001</v>
       </c>
-      <c r="E15" s="229" t="s">
+      <c r="E14" s="229" t="s">
         <v>2937</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="227"/>
-      <c r="B16" s="228"/>
-      <c r="C16" s="227"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="228"/>
+    <row r="15" spans="1:12">
+      <c r="A15" s="227"/>
+      <c r="B15" s="228"/>
+      <c r="C15" s="227"/>
+      <c r="D15" s="227"/>
+      <c r="E15" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -24833,14 +24884,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="239" t="s">
         <v>807</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -25993,15 +26044,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="239" t="s">
         <v>833</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
     </row>
     <row r="2" spans="1:7" ht="39.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -27270,28 +27321,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="240" t="s">
         <v>893</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
-      <c r="A2" s="234" t="s">
+      <c r="A2" s="235" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="236" t="s">
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="237" t="s">
         <v>894</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="G2" s="232"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
     </row>
     <row r="3" spans="1:7" ht="39.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -28319,8 +28370,8 @@
       <c r="B50" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>982</v>
+      <c r="C50" s="244" t="s">
+        <v>2939</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>983</v>
@@ -28724,7 +28775,7 @@
       <c r="D69" s="73" t="s">
         <v>1002</v>
       </c>
-      <c r="E69" s="76" t="s">
+      <c r="E69" s="72" t="s">
         <v>1005</v>
       </c>
       <c r="F69" s="75">
@@ -29688,16 +29739,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="240" t="s">
         <v>1006</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
     </row>
     <row r="2" spans="1:8" ht="39.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -32561,35 +32612,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="240" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
       <c r="I1" s="83"/>
       <c r="J1" s="83"/>
       <c r="K1" s="83"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A2" s="234" t="s">
+      <c r="A2" s="235" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="240" t="s">
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="241" t="s">
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="242" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="232"/>
+      <c r="H2" s="233"/>
       <c r="I2" s="84"/>
       <c r="J2" s="84"/>
       <c r="K2" s="84"/>
@@ -40644,29 +40695,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="239" t="s">
         <v>1183</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
       <c r="J1" s="83"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="242" t="s">
+      <c r="A2" s="243" t="s">
         <v>1184</v>
       </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="232"/>
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
       <c r="H2" s="84"/>
       <c r="I2" s="84"/>
       <c r="J2" s="84"/>
@@ -42270,29 +42321,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="239" t="s">
         <v>1264</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
       <c r="J1" s="83"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="242" t="s">
+      <c r="A2" s="243" t="s">
         <v>1265</v>
       </c>
-      <c r="B2" s="232"/>
-      <c r="C2" s="232"/>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="232"/>
+      <c r="B2" s="233"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
       <c r="H2" s="84"/>
       <c r="I2" s="84"/>
       <c r="J2" s="84"/>
